--- a/artfynd/A 36249-2022 artfynd.xlsx
+++ b/artfynd/A 36249-2022 artfynd.xlsx
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133373045</v>
+        <v>133372471</v>
       </c>
       <c r="B5" t="n">
-        <v>79412</v>
+        <v>79333</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463178</v>
+        <v>463235</v>
       </c>
       <c r="R5" t="n">
-        <v>6845360</v>
+        <v>6845215</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133372471</v>
+        <v>133373045</v>
       </c>
       <c r="B6" t="n">
-        <v>79333</v>
+        <v>79412</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463235</v>
+        <v>463178</v>
       </c>
       <c r="R6" t="n">
-        <v>6845215</v>
+        <v>6845360</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 36249-2022 artfynd.xlsx
+++ b/artfynd/A 36249-2022 artfynd.xlsx
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133372471</v>
+        <v>133373045</v>
       </c>
       <c r="B5" t="n">
-        <v>79333</v>
+        <v>79412</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463235</v>
+        <v>463178</v>
       </c>
       <c r="R5" t="n">
-        <v>6845215</v>
+        <v>6845360</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133373045</v>
+        <v>133372471</v>
       </c>
       <c r="B6" t="n">
-        <v>79412</v>
+        <v>79333</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463178</v>
+        <v>463235</v>
       </c>
       <c r="R6" t="n">
-        <v>6845360</v>
+        <v>6845215</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 36249-2022 artfynd.xlsx
+++ b/artfynd/A 36249-2022 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>133373312</v>
       </c>
       <c r="B3" t="n">
-        <v>80438</v>
+        <v>80439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>133372637</v>
       </c>
       <c r="B4" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133373045</v>
+        <v>133372471</v>
       </c>
       <c r="B5" t="n">
-        <v>79412</v>
+        <v>79334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463178</v>
+        <v>463235</v>
       </c>
       <c r="R5" t="n">
-        <v>6845360</v>
+        <v>6845215</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133372471</v>
+        <v>133373045</v>
       </c>
       <c r="B6" t="n">
-        <v>79333</v>
+        <v>79413</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463235</v>
+        <v>463178</v>
       </c>
       <c r="R6" t="n">
-        <v>6845215</v>
+        <v>6845360</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>133372757</v>
       </c>
       <c r="B7" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>133372822</v>
       </c>
       <c r="B8" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>133373669</v>
       </c>
       <c r="B9" t="n">
-        <v>80438</v>
+        <v>80439</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36249-2022 artfynd.xlsx
+++ b/artfynd/A 36249-2022 artfynd.xlsx
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133372471</v>
+        <v>133373045</v>
       </c>
       <c r="B5" t="n">
-        <v>79334</v>
+        <v>79413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463235</v>
+        <v>463178</v>
       </c>
       <c r="R5" t="n">
-        <v>6845215</v>
+        <v>6845360</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133373045</v>
+        <v>133372471</v>
       </c>
       <c r="B6" t="n">
-        <v>79413</v>
+        <v>79334</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463178</v>
+        <v>463235</v>
       </c>
       <c r="R6" t="n">
-        <v>6845360</v>
+        <v>6845215</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 36249-2022 artfynd.xlsx
+++ b/artfynd/A 36249-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133373242</v>
       </c>
       <c r="B2" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>133373312</v>
       </c>
       <c r="B3" t="n">
-        <v>80439</v>
+        <v>80453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>133372637</v>
       </c>
       <c r="B4" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133373045</v>
+        <v>133372471</v>
       </c>
       <c r="B5" t="n">
-        <v>79413</v>
+        <v>79348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463178</v>
+        <v>463235</v>
       </c>
       <c r="R5" t="n">
-        <v>6845360</v>
+        <v>6845215</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133372471</v>
+        <v>133373045</v>
       </c>
       <c r="B6" t="n">
-        <v>79334</v>
+        <v>79427</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463235</v>
+        <v>463178</v>
       </c>
       <c r="R6" t="n">
-        <v>6845215</v>
+        <v>6845360</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>133372757</v>
       </c>
       <c r="B7" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>133372822</v>
       </c>
       <c r="B8" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>133373669</v>
       </c>
       <c r="B9" t="n">
-        <v>80439</v>
+        <v>80453</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36249-2022 artfynd.xlsx
+++ b/artfynd/A 36249-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133373242</v>
       </c>
       <c r="B2" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>133373312</v>
       </c>
       <c r="B3" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>133372637</v>
       </c>
       <c r="B4" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>133372471</v>
       </c>
       <c r="B5" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>133373045</v>
       </c>
       <c r="B6" t="n">
-        <v>79427</v>
+        <v>79437</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>133372757</v>
       </c>
       <c r="B7" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>133372822</v>
       </c>
       <c r="B8" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>133373669</v>
       </c>
       <c r="B9" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36249-2022 artfynd.xlsx
+++ b/artfynd/A 36249-2022 artfynd.xlsx
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133372471</v>
+        <v>133373045</v>
       </c>
       <c r="B5" t="n">
-        <v>79358</v>
+        <v>79437</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463235</v>
+        <v>463178</v>
       </c>
       <c r="R5" t="n">
-        <v>6845215</v>
+        <v>6845360</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133373045</v>
+        <v>133372471</v>
       </c>
       <c r="B6" t="n">
-        <v>79437</v>
+        <v>79358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463178</v>
+        <v>463235</v>
       </c>
       <c r="R6" t="n">
-        <v>6845360</v>
+        <v>6845215</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 36249-2022 artfynd.xlsx
+++ b/artfynd/A 36249-2022 artfynd.xlsx
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133373045</v>
+        <v>133372471</v>
       </c>
       <c r="B5" t="n">
-        <v>79437</v>
+        <v>79358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463178</v>
+        <v>463235</v>
       </c>
       <c r="R5" t="n">
-        <v>6845360</v>
+        <v>6845215</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133372471</v>
+        <v>133373045</v>
       </c>
       <c r="B6" t="n">
-        <v>79358</v>
+        <v>79437</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463235</v>
+        <v>463178</v>
       </c>
       <c r="R6" t="n">
-        <v>6845215</v>
+        <v>6845360</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 36249-2022 artfynd.xlsx
+++ b/artfynd/A 36249-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133373242</v>
+        <v>133373045</v>
       </c>
       <c r="B2" t="n">
-        <v>57975</v>
+        <v>79452</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>463137</v>
+        <v>463178</v>
       </c>
       <c r="R2" t="n">
-        <v>6845290</v>
+        <v>6845360</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall inom anmälan.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133373312</v>
+        <v>133372471</v>
       </c>
       <c r="B3" t="n">
-        <v>80473</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>463135</v>
+        <v>463235</v>
       </c>
       <c r="R3" t="n">
-        <v>6845257</v>
+        <v>6845215</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -877,11 +872,11 @@
         <v>133372637</v>
       </c>
       <c r="B4" t="n">
-        <v>79358</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -971,14 +966,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133372471</v>
+        <v>133372757</v>
       </c>
       <c r="B5" t="n">
-        <v>79358</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>463235</v>
+        <v>463217</v>
       </c>
       <c r="R5" t="n">
-        <v>6845215</v>
+        <v>6845264</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1068,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133373045</v>
+        <v>133372822</v>
       </c>
       <c r="B6" t="n">
-        <v>79437</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,13 +1098,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463178</v>
+        <v>463212</v>
       </c>
       <c r="R6" t="n">
-        <v>6845360</v>
+        <v>6845287</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1165,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133372757</v>
+        <v>133373312</v>
       </c>
       <c r="B7" t="n">
-        <v>79358</v>
+        <v>80488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>463217</v>
+        <v>463135</v>
       </c>
       <c r="R7" t="n">
-        <v>6845264</v>
+        <v>6845257</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1262,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133372822</v>
+        <v>133373669</v>
       </c>
       <c r="B8" t="n">
-        <v>79358</v>
+        <v>80488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>463212</v>
+        <v>463223</v>
       </c>
       <c r="R8" t="n">
-        <v>6845287</v>
+        <v>6845147</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1359,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133373669</v>
+        <v>133373242</v>
       </c>
       <c r="B9" t="n">
-        <v>80473</v>
+        <v>57975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>463223</v>
+        <v>463137</v>
       </c>
       <c r="R9" t="n">
-        <v>6845147</v>
+        <v>6845290</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1430,6 +1425,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall inom anmälan.</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 36249-2022 artfynd.xlsx
+++ b/artfynd/A 36249-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133373045</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133372471</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133372637</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133372757</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133372822</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133373312</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133373669</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,8 +1493,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133373242</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>